--- a/Documentation/database documentation.xlsx
+++ b/Documentation/database documentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\NIBS\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Repos\NIBS\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DC235D-12D2-4F11-B251-28CD825BA236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42612EAE-325B-4F8A-A3F4-AECEDB8826D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{9C87F8F2-266A-41DF-B6FC-CFBFC33B3832}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{9C87F8F2-266A-41DF-B6FC-CFBFC33B3832}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="979">
   <si>
     <t>state_boundaries</t>
   </si>
@@ -2972,6 +2972,9 @@
   </si>
   <si>
     <t>vwG_National_co2e_summmary_all_gases_all_models_long</t>
+  </si>
+  <si>
+    <t>No not use to join to the data only use to overlay district boundaries when building maps.</t>
   </si>
 </sst>
 </file>
@@ -4526,6 +4529,9 @@
       <c r="B100" t="s">
         <v>142</v>
       </c>
+      <c r="C100" t="s">
+        <v>978</v>
+      </c>
       <c r="D100" t="s">
         <v>888</v>
       </c>
